--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E2">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D3">
         <v>22</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>0</v>
